--- a/3_Sample_verification/Data/UnintentionalDuplicates.xlsx
+++ b/3_Sample_verification/Data/UnintentionalDuplicates.xlsx
@@ -1,598 +1,606 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiranlee/Documents/GitHub/SeychellesWarblerGenomicToolkit/3_Sample_verification/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4C606F-9184-B240-AB05-2FF52B657102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
-  <si>
-    <t xml:space="preserve">BirdID1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filepath1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filepath2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSNPs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SexMismatchedDuplicate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SequoiaDuplicate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mismatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SnpdBoth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LLR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID1Mum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID2Mum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID1MumRel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID2MumRel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID1MumMatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdID2MumMatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdIDConsensus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BirdIDMissing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076p5/Clean_aligned/517-7626_221014_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076p4/Clean_aligned/515_GTTATTAGGC-CTCGATGAAC_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/127_CATTATCGCT-CGAGTTGCTT_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076p7/Clean_aligned/528-2526_221118_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/191-480_221007_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/190_ACGACAATGA-AACGCGGTAG_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/37-1105_221007_L004__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/21-2546_221007_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/91-931_221007_L004__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/118_ACGGCCTACA-TCTCACTCTA_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/262-2640_221014_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076p6/Clean_aligned/382-2646_TGCGTTCTGC-TTGGTCGCTC_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p4/Clean_aligned/436-2944_221111_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/103_GATCAACAAG-AAGCACTGTC_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p4/Clean_aligned/471-2899_221111_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/129_CTTCGGAATC-CGTCGGTAAG_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757/Clean_aligned/330-479_230106_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/343-573_221014_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757/Clean_aligned/336-2172_230106_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/268-4305_221014_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757/Clean_aligned/337-3290_230106_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/310-3285_221014_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/92-5614_221007_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/38-11998DH0132L01_4688_ATTCAGAAAT-TAAGATTAGT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p1raw4/Clean_aligned/619-5316_CTCGCATAGA-CGTTATCTAG_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS24675/Clean_aligned/20-11998DH0020L01_3779_GCACGGACAT-TGCGAGACGT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p1raw4/Clean_aligned/629-6032_TCCAAGTTGT-GATCTACAGG_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/131-4779_221007_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/420-4670_221118_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p2/Clean_aligned/208-4639_GTGACGCACA-CGTTGTTGCG_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/486-5264_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/48-11998DH0142L01_4849_GAATTCGTAT-GTCAGTACGT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/490-6065_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p2/Clean_aligned/216-5322_GCACTACCAG-GAAGACTTAG_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/495-5921_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/43-11998DH0137L01_4808_GAATTCGTAT-AGGATAGGGT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/497-4630_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/139-5867_221007_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/508-5936_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS24675/Clean_aligned/44-11998DH0044L01_4090_GGAGCGTCAT-GCACGGACGT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/510-4662_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p2/Clean_aligned/221-5344_GTGACACGTC-CTTACACTGA_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/534-6062_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076raw/Clean_aligned/60_CTGTCGTACA-ACTGCGAATG_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/540-4707_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/158-6027_221007_L003__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/548-4658_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/542-4791_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/550-4635_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/56-11998DH0150L01_4891_CTGAAGCTAT-GTCAGTACGT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/102_ACTTAGATCG-CGGAATTCTT_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/551-4672_221118_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/506_TGGATATGGC-TGGCGCGTAT_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076p5/Clean_aligned/508-2706_221014_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/512_ACAGAAGGTT-TGGAGATATC_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26076p5/Clean_aligned/514-7970_221014_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/542_ACTTGACTAG-GTATCAACGG_L001__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/fastdata/bop21kgl/RawData/LIMS26629p4/Clean_aligned/496-2338_221111_L002__all_mapped_rehead.bam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="191">
+  <si>
+    <t>BirdID1</t>
+  </si>
+  <si>
+    <t>Filepath1</t>
+  </si>
+  <si>
+    <t>BirdID2</t>
+  </si>
+  <si>
+    <t>Filepath2</t>
+  </si>
+  <si>
+    <t>NSNPs</t>
+  </si>
+  <si>
+    <t>V6</t>
+  </si>
+  <si>
+    <t>V7</t>
+  </si>
+  <si>
+    <t>Kinship</t>
+  </si>
+  <si>
+    <t>SexMismatchedDuplicate</t>
+  </si>
+  <si>
+    <t>SequoiaDuplicate</t>
+  </si>
+  <si>
+    <t>Mismatch</t>
+  </si>
+  <si>
+    <t>SnpdBoth</t>
+  </si>
+  <si>
+    <t>LLR</t>
+  </si>
+  <si>
+    <t>BirdID1Mum</t>
+  </si>
+  <si>
+    <t>BirdID2Mum</t>
+  </si>
+  <si>
+    <t>BirdID1MumRel</t>
+  </si>
+  <si>
+    <t>BirdID2MumRel</t>
+  </si>
+  <si>
+    <t>BirdID1MumMatch</t>
+  </si>
+  <si>
+    <t>BirdID2MumMatch</t>
+  </si>
+  <si>
+    <t>BirdIDConsensus</t>
+  </si>
+  <si>
+    <t>BirdIDMissing</t>
+  </si>
+  <si>
+    <t>6862</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076p5/Clean_aligned/517-7626_221014_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6670</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076p4/Clean_aligned/515_GTTATTAGGC-CTCGATGAAC_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>4965</t>
+  </si>
+  <si>
+    <t>5596</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/127_CATTATCGCT-CGAGTTGCTT_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076p7/Clean_aligned/528-2526_221118_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>774</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/191-480_221007_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3459</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/190_ACGACAATGA-AACGCGGTAG_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>853</t>
+  </si>
+  <si>
+    <t>1275</t>
+  </si>
+  <si>
+    <t>P1only</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>1218</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/37-1105_221007_L004__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/21-2546_221007_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p2/Clean_aligned/91-931_221007_L004__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1499</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/118_ACGGCCTACA-TCTCACTCTA_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>595</t>
+  </si>
+  <si>
+    <t>670</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/262-2640_221014_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1303</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076p6/Clean_aligned/382-2646_TGCGTTCTGC-TTGGTCGCTC_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>P2only</t>
+  </si>
+  <si>
+    <t>3695</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p4/Clean_aligned/436-2944_221111_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1271</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/103_GATCAACAAG-AAGCACTGTC_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1437</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>3643</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p4/Clean_aligned/471-2899_221111_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>4882</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629/Clean_aligned/129_CTTCGGAATC-CGTCGGTAAG_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1665</t>
+  </si>
+  <si>
+    <t>3086</t>
+  </si>
+  <si>
+    <t>3017</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757/Clean_aligned/330-479_230106_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3503</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/343-573_221014_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>1536</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757/Clean_aligned/336-2172_230106_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3444</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/268-4305_221014_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1764</t>
+  </si>
+  <si>
+    <t>4889</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757/Clean_aligned/337-3290_230106_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>4933</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p3/Clean_aligned/310-3285_221014_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1740</t>
+  </si>
+  <si>
+    <t>3453</t>
+  </si>
+  <si>
+    <t>4883</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/92-5614_221007_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/38-11998DH0132L01_4688_ATTCAGAAAT-TAAGATTAGT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1697</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>5585</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p1raw4/Clean_aligned/619-5316_CTCGCATAGA-CGTTATCTAG_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5613</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS24675/Clean_aligned/20-11998DH0020L01_3779_GCACGGACAT-TGCGAGACGT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5164</t>
+  </si>
+  <si>
+    <t>3518</t>
+  </si>
+  <si>
+    <t>6145</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p1raw4/Clean_aligned/629-6032_TCCAAGTTGT-GATCTACAGG_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5636</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/131-4779_221007_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5514</t>
+  </si>
+  <si>
+    <t>5336</t>
+  </si>
+  <si>
+    <t>4961</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/420-4670_221118_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5550</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p2/Clean_aligned/208-4639_GTGACGCACA-CGTTGTTGCG_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1361</t>
+  </si>
+  <si>
+    <t>4896</t>
+  </si>
+  <si>
+    <t>5828</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/486-5264_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5624</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/48-11998DH0142L01_4849_GAATTCGTAT-GTCAGTACGT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3002</t>
+  </si>
+  <si>
+    <t>5533</t>
+  </si>
+  <si>
+    <t>6150</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/490-6065_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5786</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p2/Clean_aligned/216-5322_GCACTACCAG-GAAGACTTAG_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6028</t>
+  </si>
+  <si>
+    <t>1763</t>
+  </si>
+  <si>
+    <t>6158</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/495-5921_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6142</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/43-11998DH0137L01_4808_GAATTCGTAT-AGGATAGGGT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5598</t>
+  </si>
+  <si>
+    <t>5604</t>
+  </si>
+  <si>
+    <t>5542</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/497-4630_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6136</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/139-5867_221007_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3569</t>
+  </si>
+  <si>
+    <t>3085</t>
+  </si>
+  <si>
+    <t>6165</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/508-5936_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5516</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS24675/Clean_aligned/44-11998DH0044L01_4090_GGAGCGTCAT-GCACGGACGT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6066</t>
+  </si>
+  <si>
+    <t>1864</t>
+  </si>
+  <si>
+    <t>5567</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/510-4662_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5529</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p2/Clean_aligned/221-5344_GTGACACGTC-CTTACACTGA_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3604</t>
+  </si>
+  <si>
+    <t>3698</t>
+  </si>
+  <si>
+    <t>6176</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/534-6062_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5551</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076raw/Clean_aligned/60_CTGTCGTACA-ACTGCGAATG_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3567</t>
+  </si>
+  <si>
+    <t>5586</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/540-4707_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6140</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p1/Clean_aligned/158-6027_221007_L003__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>5625</t>
+  </si>
+  <si>
+    <t>5563</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/548-4658_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>5528</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/542-4791_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>4960</t>
+  </si>
+  <si>
+    <t>5546</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/550-4635_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>6175</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS25133/Clean_aligned/56-11998DH0150L01_4891_CTGAAGCTAT-GTCAGTACGT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>4936</t>
+  </si>
+  <si>
+    <t>4904</t>
+  </si>
+  <si>
+    <t>1276</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/102_ACTTAGATCG-CGGAATTCTT_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1765</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26757p3/Clean_aligned/551-4672_221118_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/506_TGGATATGGC-TGGCGCGTAT_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>3871</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076p5/Clean_aligned/508-2706_221014_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>1542</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/512_ACAGAAGGTT-TGGAGATATC_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>7082</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26076p5/Clean_aligned/514-7970_221014_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>6217</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMSMERGED/Clean_aligned/542_ACTTGACTAG-GTATCAACGG_L001__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>890</t>
+  </si>
+  <si>
+    <t>/fastdata/bop21kgl/RawData/LIMS26629p4/Clean_aligned/496-2338_221111_L002__all_mapped_rehead.bam</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>199</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -628,6 +636,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -909,11 +926,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -978,7 +995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -991,17 +1008,17 @@
       <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>486991</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.420244</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.499963</v>
+      <c r="F2">
+        <v>0.42024400000000001</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0.49996299999999999</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -1009,14 +1026,14 @@
       <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>572</v>
       </c>
-      <c r="M2" t="n">
-        <v>114.579952045039</v>
+      <c r="M2">
+        <v>114.57995204503899</v>
       </c>
       <c r="N2" t="s">
         <v>25</v>
@@ -1024,11 +1041,11 @@
       <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" t="n">
-        <v>-0.0303754</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.00447138</v>
+      <c r="P2">
+        <v>-3.03754E-2</v>
+      </c>
+      <c r="Q2">
+        <v>4.4713799999999996E-3</v>
       </c>
       <c r="R2" t="s">
         <v>10</v>
@@ -1043,7 +1060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1056,17 +1073,17 @@
       <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>486805</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.410844</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.499933</v>
+      <c r="F3">
+        <v>0.41084399999999999</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0.49993300000000002</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -1074,23 +1091,21 @@
       <c r="J3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>571</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>118.123528006068</v>
       </c>
       <c r="N3" t="s">
         <v>31</v>
       </c>
-      <c r="O3"/>
-      <c r="P3" t="n">
-        <v>-0.0384707</v>
-      </c>
-      <c r="Q3"/>
+      <c r="P3">
+        <v>-3.8470699999999997E-2</v>
+      </c>
       <c r="R3" t="s">
         <v>10</v>
       </c>
@@ -1104,7 +1119,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1117,17 +1132,17 @@
       <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>486627</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.438747</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.499922</v>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0.49992199999999998</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1135,13 +1150,13 @@
       <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>572</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>116.774560829392</v>
       </c>
       <c r="N4" t="s">
@@ -1150,10 +1165,10 @@
       <c r="O4" t="s">
         <v>38</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.0395877</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="P4">
+        <v>3.9587700000000003E-2</v>
+      </c>
+      <c r="Q4">
         <v>0.568303</v>
       </c>
       <c r="R4" t="s">
@@ -1169,7 +1184,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1182,17 +1197,17 @@
       <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>486966</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.448241</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.499943</v>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0.49994300000000003</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1200,22 +1215,20 @@
       <c r="J5" t="b">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>572</v>
       </c>
-      <c r="M5" t="n">
-        <v>120.044243378024</v>
-      </c>
-      <c r="N5"/>
+      <c r="M5">
+        <v>120.04424337802401</v>
+      </c>
       <c r="O5" t="s">
         <v>45</v>
       </c>
-      <c r="P5"/>
-      <c r="Q5" t="n">
-        <v>0.0221868</v>
+      <c r="Q5">
+        <v>2.21868E-2</v>
       </c>
       <c r="R5" t="s">
         <v>32</v>
@@ -1230,7 +1243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -1243,17 +1256,17 @@
       <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>486976</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.512623</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.499786</v>
+      <c r="F6">
+        <v>0.51262300000000005</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0.49978600000000001</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1261,13 +1274,13 @@
       <c r="J6" t="b">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>572</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>124.179540297751</v>
       </c>
       <c r="N6" t="s">
@@ -1276,11 +1289,11 @@
       <c r="O6" t="s">
         <v>51</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.0583732</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.0317513</v>
+      <c r="P6">
+        <v>5.83732E-2</v>
+      </c>
+      <c r="Q6">
+        <v>-3.1751300000000003E-2</v>
       </c>
       <c r="R6" t="s">
         <v>40</v>
@@ -1295,7 +1308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -1308,17 +1321,17 @@
       <c r="D7" t="s">
         <v>55</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>486590</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.428698</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.499752</v>
+      <c r="F7">
+        <v>0.42869800000000002</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.49975199999999997</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -1326,21 +1339,18 @@
       <c r="J7" t="b">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
         <v>569</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>112.066892889502</v>
       </c>
       <c r="N7" t="s">
         <v>56</v>
       </c>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7"/>
       <c r="R7" t="s">
         <v>39</v>
       </c>
@@ -1354,7 +1364,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -1367,16 +1377,16 @@
       <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>486976</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.480861</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="F8">
+        <v>0.48086099999999998</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>0.499948</v>
       </c>
       <c r="I8" t="b">
@@ -1385,14 +1395,14 @@
       <c r="J8" t="b">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>572</v>
       </c>
-      <c r="M8" t="n">
-        <v>123.74900850279</v>
+      <c r="M8">
+        <v>123.74900850279001</v>
       </c>
       <c r="N8" t="s">
         <v>62</v>
@@ -1400,11 +1410,11 @@
       <c r="O8" t="s">
         <v>63</v>
       </c>
-      <c r="P8" t="n">
-        <v>0.502955</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.0970294</v>
+      <c r="P8">
+        <v>0.50295500000000004</v>
+      </c>
+      <c r="Q8">
+        <v>-9.7029400000000002E-2</v>
       </c>
       <c r="R8" t="s">
         <v>10</v>
@@ -1419,7 +1429,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1432,17 +1442,17 @@
       <c r="D9" t="s">
         <v>67</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>486962</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.43428</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.499952</v>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0.49995200000000001</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -1450,14 +1460,14 @@
       <c r="J9" t="b">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>572</v>
       </c>
-      <c r="M9" t="n">
-        <v>118.004455971072</v>
+      <c r="M9">
+        <v>118.00445597107201</v>
       </c>
       <c r="N9" t="s">
         <v>68</v>
@@ -1465,11 +1475,11 @@
       <c r="O9" t="s">
         <v>69</v>
       </c>
-      <c r="P9" t="n">
-        <v>0.508757</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.037779</v>
+      <c r="P9">
+        <v>0.50875700000000001</v>
+      </c>
+      <c r="Q9">
+        <v>-3.7779E-2</v>
       </c>
       <c r="R9" t="s">
         <v>40</v>
@@ -1484,7 +1494,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1497,17 +1507,17 @@
       <c r="D10" t="s">
         <v>73</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>486675</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.518216</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.499508</v>
+      <c r="F10">
+        <v>0.51821600000000001</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0.49950800000000001</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -1515,13 +1525,13 @@
       <c r="J10" t="b">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>571</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>106.125535014806</v>
       </c>
       <c r="N10" t="s">
@@ -1530,11 +1540,11 @@
       <c r="O10" t="s">
         <v>75</v>
       </c>
-      <c r="P10" t="n">
-        <v>0.437659</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.0221078</v>
+      <c r="P10">
+        <v>0.43765900000000002</v>
+      </c>
+      <c r="Q10">
+        <v>2.21078E-2</v>
       </c>
       <c r="R10" t="s">
         <v>40</v>
@@ -1549,7 +1559,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -1562,17 +1572,17 @@
       <c r="D11" t="s">
         <v>79</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>486658</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.515214</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.49957</v>
+      <c r="F11">
+        <v>0.51521399999999995</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0.49957000000000001</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1580,22 +1590,20 @@
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>572</v>
       </c>
-      <c r="M11" t="n">
-        <v>121.884482634437</v>
-      </c>
-      <c r="N11"/>
+      <c r="M11">
+        <v>121.88448263443701</v>
+      </c>
       <c r="O11" t="s">
         <v>80</v>
       </c>
-      <c r="P11"/>
-      <c r="Q11" t="n">
-        <v>0.593124</v>
+      <c r="Q11">
+        <v>0.59312399999999998</v>
       </c>
       <c r="R11" t="s">
         <v>32</v>
@@ -1610,7 +1618,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>81</v>
       </c>
@@ -1623,16 +1631,16 @@
       <c r="D12" t="s">
         <v>84</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>486797</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.463906</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="F12">
+        <v>0.46390599999999999</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>0.499776</v>
       </c>
       <c r="I12" t="b">
@@ -1641,13 +1649,13 @@
       <c r="J12" t="b">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
         <v>572</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>118.568229328358</v>
       </c>
       <c r="N12" t="s">
@@ -1656,11 +1664,11 @@
       <c r="O12" t="s">
         <v>86</v>
       </c>
-      <c r="P12" t="n">
-        <v>-0.0131951</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.443056</v>
+      <c r="P12">
+        <v>-1.31951E-2</v>
+      </c>
+      <c r="Q12">
+        <v>0.44305600000000001</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -1675,7 +1683,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1688,17 +1696,17 @@
       <c r="D13" t="s">
         <v>90</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>487053</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.449312</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.499986</v>
+      <c r="F13">
+        <v>0.44931199999999999</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0.49998599999999999</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1706,13 +1714,13 @@
       <c r="J13" t="b">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>572</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>120.092086595712</v>
       </c>
       <c r="N13" t="s">
@@ -1721,11 +1729,11 @@
       <c r="O13" t="s">
         <v>92</v>
       </c>
-      <c r="P13" t="n">
-        <v>-0.00587665</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.43475</v>
+      <c r="P13">
+        <v>-5.8766499999999998E-3</v>
+      </c>
+      <c r="Q13">
+        <v>0.43475000000000003</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -1740,7 +1748,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1753,17 +1761,17 @@
       <c r="D14" t="s">
         <v>96</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>487054</v>
       </c>
-      <c r="F14" t="n">
-        <v>0.456576</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.499963</v>
+      <c r="F14">
+        <v>0.45657599999999998</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0.49996299999999999</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1771,13 +1779,13 @@
       <c r="J14" t="b">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>572</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>118.94140750664</v>
       </c>
       <c r="N14" t="s">
@@ -1786,11 +1794,11 @@
       <c r="O14" t="s">
         <v>98</v>
       </c>
-      <c r="P14" t="n">
-        <v>0.00844709</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.0243502</v>
+      <c r="P14">
+        <v>8.4470900000000008E-3</v>
+      </c>
+      <c r="Q14">
+        <v>-2.4350199999999999E-2</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -1805,7 +1813,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -1818,17 +1826,17 @@
       <c r="D15" t="s">
         <v>102</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>487012</v>
       </c>
-      <c r="F15" t="n">
-        <v>0.509148</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.499922</v>
+      <c r="F15">
+        <v>0.50914800000000004</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0.49992199999999998</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -1836,13 +1844,13 @@
       <c r="J15" t="b">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>572</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>123.890053269123</v>
       </c>
       <c r="N15" t="s">
@@ -1851,11 +1859,11 @@
       <c r="O15" t="s">
         <v>104</v>
       </c>
-      <c r="P15" t="n">
-        <v>0.0816856</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.022907</v>
+      <c r="P15">
+        <v>8.1685599999999997E-2</v>
+      </c>
+      <c r="Q15">
+        <v>2.2907E-2</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -1870,7 +1878,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>105</v>
       </c>
@@ -1883,17 +1891,17 @@
       <c r="D16" t="s">
         <v>108</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>486309</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.519705</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.499597</v>
+      <c r="F16">
+        <v>0.51970499999999997</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0.49959700000000001</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -1901,14 +1909,14 @@
       <c r="J16" t="b">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>569</v>
       </c>
-      <c r="M16" t="n">
-        <v>111.019664711539</v>
+      <c r="M16">
+        <v>111.01966471153899</v>
       </c>
       <c r="N16" t="s">
         <v>109</v>
@@ -1916,11 +1924,11 @@
       <c r="O16" t="s">
         <v>110</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>0.432811</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.0129075</v>
+      <c r="Q16">
+        <v>-1.2907500000000001E-2</v>
       </c>
       <c r="R16" t="s">
         <v>40</v>
@@ -1935,7 +1943,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>111</v>
       </c>
@@ -1948,16 +1956,16 @@
       <c r="D17" t="s">
         <v>114</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>486869</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.476941</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>0.499857</v>
       </c>
       <c r="I17" t="b">
@@ -1966,13 +1974,13 @@
       <c r="J17" t="b">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>571</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>126.588197886955</v>
       </c>
       <c r="N17" t="s">
@@ -1981,11 +1989,11 @@
       <c r="O17" t="s">
         <v>116</v>
       </c>
-      <c r="P17" t="n">
-        <v>0.0317477</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.359829</v>
+      <c r="P17">
+        <v>3.1747699999999997E-2</v>
+      </c>
+      <c r="Q17">
+        <v>0.35982900000000001</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -2000,7 +2008,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>117</v>
       </c>
@@ -2013,17 +2021,17 @@
       <c r="D18" t="s">
         <v>120</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>486704</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.471471</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.49968</v>
+      <c r="F18">
+        <v>0.47147099999999997</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0.49968000000000001</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -2031,14 +2039,14 @@
       <c r="J18" t="b">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <v>571</v>
       </c>
-      <c r="M18" t="n">
-        <v>122.523782506924</v>
+      <c r="M18">
+        <v>122.52378250692399</v>
       </c>
       <c r="N18" t="s">
         <v>121</v>
@@ -2046,11 +2054,11 @@
       <c r="O18" t="s">
         <v>122</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>0.187387</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0.510213</v>
+      <c r="Q18">
+        <v>0.51021300000000003</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -2065,7 +2073,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>123</v>
       </c>
@@ -2078,17 +2086,17 @@
       <c r="D19" t="s">
         <v>126</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>486740</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.432091</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.499916</v>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0.49991600000000003</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -2096,13 +2104,13 @@
       <c r="J19" t="b">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <v>572</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>118.428899430654</v>
       </c>
       <c r="N19" t="s">
@@ -2111,10 +2119,10 @@
       <c r="O19" t="s">
         <v>128</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.00100032</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="P19">
+        <v>1.0003200000000001E-3</v>
+      </c>
+      <c r="Q19">
         <v>0.478487</v>
       </c>
       <c r="R19" t="s">
@@ -2123,10 +2131,8 @@
       <c r="S19" t="s">
         <v>39</v>
       </c>
-      <c r="T19"/>
-      <c r="U19"/>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>129</v>
       </c>
@@ -2139,17 +2145,17 @@
       <c r="D20" t="s">
         <v>132</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>486402</v>
       </c>
-      <c r="F20" t="n">
-        <v>0.512498</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.499806</v>
+      <c r="F20">
+        <v>0.51249800000000001</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.49980599999999997</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -2157,13 +2163,13 @@
       <c r="J20" t="b">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
         <v>570</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>118.805235002004</v>
       </c>
       <c r="N20" t="s">
@@ -2172,11 +2178,11 @@
       <c r="O20" t="s">
         <v>134</v>
       </c>
-      <c r="P20" t="n">
-        <v>0.25251</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.489361</v>
+      <c r="P20">
+        <v>0.25251000000000001</v>
+      </c>
+      <c r="Q20">
+        <v>0.48936099999999999</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -2191,7 +2197,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>135</v>
       </c>
@@ -2204,17 +2210,17 @@
       <c r="D21" t="s">
         <v>138</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>486865</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.476662</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.499876</v>
+      <c r="F21">
+        <v>0.47666199999999997</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0.49987599999999999</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -2222,14 +2228,14 @@
       <c r="J21" t="b">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>572</v>
       </c>
-      <c r="M21" t="n">
-        <v>119.994886651319</v>
+      <c r="M21">
+        <v>119.99488665131901</v>
       </c>
       <c r="N21" t="s">
         <v>139</v>
@@ -2237,11 +2243,11 @@
       <c r="O21" t="s">
         <v>140</v>
       </c>
-      <c r="P21" t="n">
-        <v>-0.0476732</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-0.0455503</v>
+      <c r="P21">
+        <v>-4.7673199999999999E-2</v>
+      </c>
+      <c r="Q21">
+        <v>-4.5550300000000002E-2</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -2256,7 +2262,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>141</v>
       </c>
@@ -2269,17 +2275,17 @@
       <c r="D22" t="s">
         <v>144</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>486263</v>
       </c>
-      <c r="F22" t="n">
-        <v>0.396156</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.499236</v>
+      <c r="F22">
+        <v>0.39615600000000001</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0.49923600000000001</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -2287,14 +2293,14 @@
       <c r="J22" t="b">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>569</v>
       </c>
-      <c r="M22" t="n">
-        <v>99.4590735916761</v>
+      <c r="M22">
+        <v>99.459073591676102</v>
       </c>
       <c r="N22" t="s">
         <v>145</v>
@@ -2302,11 +2308,11 @@
       <c r="O22" t="s">
         <v>146</v>
       </c>
-      <c r="P22" t="n">
-        <v>-0.0509961</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-0.0549005</v>
+      <c r="P22">
+        <v>-5.0996100000000003E-2</v>
+      </c>
+      <c r="Q22">
+        <v>-5.4900499999999998E-2</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -2321,7 +2327,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -2334,17 +2340,17 @@
       <c r="D23" t="s">
         <v>150</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>485213</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.48123</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.499653</v>
+      <c r="F23">
+        <v>0.48122999999999999</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0.49965300000000001</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -2352,14 +2358,14 @@
       <c r="J23" t="b">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
         <v>570</v>
       </c>
-      <c r="M23" t="n">
-        <v>120.467921566284</v>
+      <c r="M23">
+        <v>120.46792156628401</v>
       </c>
       <c r="N23" t="s">
         <v>25</v>
@@ -2367,11 +2373,11 @@
       <c r="O23" t="s">
         <v>151</v>
       </c>
-      <c r="P23" t="n">
-        <v>-0.0421482</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.0291127</v>
+      <c r="P23">
+        <v>-4.2148199999999997E-2</v>
+      </c>
+      <c r="Q23">
+        <v>2.9112699999999998E-2</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -2386,7 +2392,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>152</v>
       </c>
@@ -2399,17 +2405,17 @@
       <c r="D24" t="s">
         <v>155</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>483488</v>
       </c>
-      <c r="F24" t="n">
-        <v>0.500021</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.49868</v>
+      <c r="F24">
+        <v>0.50002100000000005</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0.49868000000000001</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -2417,13 +2423,13 @@
       <c r="J24" t="b">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>5</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>565</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>102.652752368134</v>
       </c>
       <c r="N24" t="s">
@@ -2432,11 +2438,11 @@
       <c r="O24" t="s">
         <v>157</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>0.451797</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-0.0167737</v>
+      <c r="Q24">
+        <v>-1.6773699999999999E-2</v>
       </c>
       <c r="R24" t="s">
         <v>40</v>
@@ -2451,7 +2457,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>158</v>
       </c>
@@ -2464,17 +2470,17 @@
       <c r="D25" t="s">
         <v>161</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>486624</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.515603</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.49973</v>
+      <c r="F25">
+        <v>0.51560300000000003</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0.49973000000000001</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -2482,13 +2488,13 @@
       <c r="J25" t="b">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>570</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>123.133753549115</v>
       </c>
       <c r="N25" t="s">
@@ -2497,10 +2503,10 @@
       <c r="O25" t="s">
         <v>162</v>
       </c>
-      <c r="P25" t="n">
-        <v>-0.0494896</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="P25">
+        <v>-4.9489600000000002E-2</v>
+      </c>
+      <c r="Q25">
         <v>-0.133465</v>
       </c>
       <c r="R25" t="s">
@@ -2516,7 +2522,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>163</v>
       </c>
@@ -2529,17 +2535,17 @@
       <c r="D26" t="s">
         <v>166</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>486793</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.49412</v>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.499814</v>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0.49981399999999998</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
@@ -2547,13 +2553,13 @@
       <c r="J26" t="b">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
         <v>572</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>123.614716199368</v>
       </c>
       <c r="N26" t="s">
@@ -2562,11 +2568,11 @@
       <c r="O26" t="s">
         <v>168</v>
       </c>
-      <c r="P26" t="n">
-        <v>-0.0209709</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.40643</v>
+      <c r="P26">
+        <v>-2.0970900000000001E-2</v>
+      </c>
+      <c r="Q26">
+        <v>0.40643000000000001</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -2581,7 +2587,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>169</v>
       </c>
@@ -2594,17 +2600,17 @@
       <c r="D27" t="s">
         <v>172</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>486810</v>
       </c>
-      <c r="F27" t="n">
-        <v>0.4323</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.499867</v>
+      <c r="F27">
+        <v>0.43230000000000002</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0.49986700000000001</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
@@ -2612,13 +2618,13 @@
       <c r="J27" t="b">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
         <v>572</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>113.915818625344</v>
       </c>
       <c r="N27" t="s">
@@ -2627,11 +2633,11 @@
       <c r="O27" t="s">
         <v>173</v>
       </c>
-      <c r="P27" t="n">
-        <v>-0.0435831</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.538521</v>
+      <c r="P27">
+        <v>-4.35831E-2</v>
+      </c>
+      <c r="Q27">
+        <v>0.53852100000000003</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -2646,7 +2652,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>174</v>
       </c>
@@ -2659,16 +2665,16 @@
       <c r="D28" t="s">
         <v>177</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>486990</v>
       </c>
-      <c r="F28" t="n">
-        <v>0.422187</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="F28">
+        <v>0.42218699999999998</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
         <v>0.499944</v>
       </c>
       <c r="I28" t="b">
@@ -2677,21 +2683,18 @@
       <c r="J28" t="b">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>572</v>
       </c>
-      <c r="M28" t="n">
-        <v>117.540830364663</v>
-      </c>
-      <c r="N28"/>
+      <c r="M28">
+        <v>117.54083036466299</v>
+      </c>
       <c r="O28" t="s">
         <v>178</v>
       </c>
-      <c r="P28"/>
-      <c r="Q28"/>
       <c r="R28" t="s">
         <v>57</v>
       </c>
@@ -2705,7 +2708,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>179</v>
       </c>
@@ -2718,17 +2721,17 @@
       <c r="D29" t="s">
         <v>182</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>467244</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.433758</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.498318</v>
+      <c r="F29">
+        <v>0.43375799999999998</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0.49831799999999998</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -2736,13 +2739,13 @@
       <c r="J29" t="b">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>529</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>105.444526368133</v>
       </c>
       <c r="N29" t="s">
@@ -2751,11 +2754,11 @@
       <c r="O29" t="s">
         <v>184</v>
       </c>
-      <c r="P29" t="n">
-        <v>0.433383</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.013619</v>
+      <c r="P29">
+        <v>0.43338300000000002</v>
+      </c>
+      <c r="Q29">
+        <v>1.3618999999999999E-2</v>
       </c>
       <c r="R29" t="s">
         <v>40</v>
@@ -2770,7 +2773,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -2783,17 +2786,17 @@
       <c r="D30" t="s">
         <v>188</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>486925</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.493177</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.49997</v>
+      <c r="F30">
+        <v>0.49317699999999998</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0.49997000000000003</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -2801,13 +2804,13 @@
       <c r="J30" t="b">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
         <v>572</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>126.076687358914</v>
       </c>
       <c r="N30" t="s">
@@ -2816,10 +2819,10 @@
       <c r="O30" t="s">
         <v>190</v>
       </c>
-      <c r="P30" t="n">
-        <v>0.765195</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="P30">
+        <v>0.76519499999999996</v>
+      </c>
+      <c r="Q30">
         <v>-0.103468</v>
       </c>
       <c r="R30" t="s">
@@ -2837,6 +2840,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334CAF14-1E01-BC4F-A84D-03F2AA5EFA2B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>